--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="116">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -82,6 +85,54 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>1178 Русе, бул. България</t>
+  </si>
+  <si>
+    <t>1161 София Шипченски проход</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1134 Монтана</t>
+  </si>
+  <si>
+    <t>1164 София Д. Богров</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
     <t>СВ2201СС</t>
   </si>
   <si>
@@ -118,49 +169,181 @@
     <t>ADBLUE 1L</t>
   </si>
   <si>
-    <t>13:41</t>
-  </si>
-  <si>
-    <t>15:46</t>
-  </si>
-  <si>
-    <t>15:28</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>14:36</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>05:56</t>
-  </si>
-  <si>
-    <t>11:01</t>
-  </si>
-  <si>
-    <t>11:49</t>
-  </si>
-  <si>
-    <t>01:13</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>06:22</t>
-  </si>
-  <si>
-    <t>18:13</t>
-  </si>
-  <si>
-    <t>23:21</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:41:00</t>
+  </si>
+  <si>
+    <t>15:46:00</t>
+  </si>
+  <si>
+    <t>15:28:00</t>
+  </si>
+  <si>
+    <t>06:22:00</t>
+  </si>
+  <si>
+    <t>14:36:00</t>
+  </si>
+  <si>
+    <t>19:50:00</t>
+  </si>
+  <si>
+    <t>01:21:00</t>
+  </si>
+  <si>
+    <t>05:56:00</t>
+  </si>
+  <si>
+    <t>11:01:00</t>
+  </si>
+  <si>
+    <t>11:47:00</t>
+  </si>
+  <si>
+    <t>01:14:00</t>
+  </si>
+  <si>
+    <t>21:20:00</t>
+  </si>
+  <si>
+    <t>06:23:00</t>
+  </si>
+  <si>
+    <t>18:12:00</t>
+  </si>
+  <si>
+    <t>23:21:00</t>
+  </si>
+  <si>
+    <t>20:16:00</t>
+  </si>
+  <si>
+    <t>06:42:00</t>
+  </si>
+  <si>
+    <t>16:05:00</t>
+  </si>
+  <si>
+    <t>16:19:00</t>
+  </si>
+  <si>
+    <t>07:32:00</t>
+  </si>
+  <si>
+    <t>18:49:00</t>
+  </si>
+  <si>
+    <t>18:34:00</t>
+  </si>
+  <si>
+    <t>18:32:00</t>
+  </si>
+  <si>
+    <t>15:47:00</t>
+  </si>
+  <si>
+    <t>16:42:00</t>
+  </si>
+  <si>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>07:36:00</t>
+  </si>
+  <si>
+    <t>10:14:00</t>
+  </si>
+  <si>
+    <t>13:58:00</t>
+  </si>
+  <si>
+    <t>3231295050 3231295050</t>
+  </si>
+  <si>
+    <t>3231466737 3231466737</t>
+  </si>
+  <si>
+    <t>3231517174 3231517174</t>
+  </si>
+  <si>
+    <t>3231536044 3231536044</t>
+  </si>
+  <si>
+    <t>3231599446 3231599446</t>
+  </si>
+  <si>
+    <t>3231604982 3231604982</t>
+  </si>
+  <si>
+    <t>3231744746 3231744746</t>
+  </si>
+  <si>
+    <t>3231764479 3231764479</t>
+  </si>
+  <si>
+    <t>3231776837 3231776837</t>
+  </si>
+  <si>
+    <t>3231814383 3231814383</t>
+  </si>
+  <si>
+    <t>3231798520 3231798520</t>
+  </si>
+  <si>
+    <t>3231834645 3231834645</t>
+  </si>
+  <si>
+    <t>3231894644 3231894644</t>
+  </si>
+  <si>
+    <t>3231939640 3231939640</t>
+  </si>
+  <si>
+    <t>3231939874 3231939874</t>
+  </si>
+  <si>
+    <t>3232069135 3232069135</t>
+  </si>
+  <si>
+    <t>3232086497 3232086497</t>
+  </si>
+  <si>
+    <t>3232111191 3232111191</t>
+  </si>
+  <si>
+    <t>3232109631 3232109631</t>
+  </si>
+  <si>
+    <t>3232187445 3232187445</t>
+  </si>
+  <si>
+    <t>3232209903 3232209903</t>
+  </si>
+  <si>
+    <t>3232261226 3232261226</t>
+  </si>
+  <si>
+    <t>3232258092 3232258092</t>
+  </si>
+  <si>
+    <t>3232260736 3232260736</t>
+  </si>
+  <si>
+    <t>3232434412 3232434412</t>
+  </si>
+  <si>
+    <t>3232449826 3232449826</t>
+  </si>
+  <si>
+    <t>3232476859 3232476859</t>
+  </si>
+  <si>
+    <t>3232530470 3232530470</t>
+  </si>
+  <si>
+    <t>3232607338 3232607338</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЕВРОУЕЙ СЪРВИЗ ООД</t>
@@ -584,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -593,16 +776,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -642,836 +826,1553 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1178</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F2">
         <v>58.13</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2">
         <v>1.64</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>95.33</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>104.63</v>
       </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>52</v>
       </c>
       <c r="M2">
-        <v>102662</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1178</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="F3">
+        <v>215</v>
+      </c>
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3">
+        <v>1.64</v>
+      </c>
+      <c r="I3" s="1">
+        <v>352.6</v>
+      </c>
+      <c r="J3">
+        <v>1.8</v>
+      </c>
+      <c r="K3" s="1">
+        <v>387</v>
+      </c>
+      <c r="L3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4">
         <v>26.02</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4">
         <v>1.22</v>
       </c>
-      <c r="H3">
+      <c r="I4" s="1">
         <v>31.74</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J4">
         <v>1.22</v>
       </c>
-      <c r="J3">
+      <c r="K4" s="1">
         <v>31.74</v>
       </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>103822</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>1178</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4">
-        <v>215</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="H4">
-        <v>352.6</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J4">
-        <v>387</v>
-      </c>
-      <c r="K4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="L4" t="s">
+        <v>53</v>
       </c>
       <c r="M4">
-        <v>103822</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1178</v>
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F5">
         <v>175</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5">
         <v>1.64</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>287</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>315</v>
       </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>54</v>
       </c>
       <c r="M5">
-        <v>104131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1161</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F6">
         <v>250</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6">
         <v>1.64</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>410</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.8</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>450</v>
       </c>
-      <c r="K6" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+      <c r="L6" t="s">
+        <v>55</v>
       </c>
       <c r="M6">
-        <v>40533</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1178</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>230.1</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7">
         <v>1.63</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>375.06</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.79</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>411.88</v>
       </c>
-      <c r="K7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
+      <c r="L7" t="s">
+        <v>56</v>
       </c>
       <c r="M7">
-        <v>104674</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>1178</v>
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F8">
         <v>69.16</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8">
         <v>1.63</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>112.73</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.79</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>123.8</v>
       </c>
-      <c r="K8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+      <c r="L8" t="s">
+        <v>57</v>
       </c>
       <c r="M8">
-        <v>104886</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9">
-        <v>1147</v>
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F9">
         <v>105.75</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9">
         <v>1.63</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>172.37</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.79</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>189.29</v>
       </c>
-      <c r="K9" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
+      <c r="L9" t="s">
+        <v>58</v>
       </c>
       <c r="M9">
-        <v>179397</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10">
-        <v>1147</v>
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F10">
         <v>240.08</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10">
         <v>1.62</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>388.93</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.79</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>429.74</v>
       </c>
-      <c r="K10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" t="s">
+        <v>59</v>
       </c>
       <c r="M10">
-        <v>179898</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11">
-        <v>1198</v>
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="F11">
+        <v>375</v>
+      </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11">
+        <v>1.62</v>
+      </c>
+      <c r="I11" s="1">
+        <v>607.5</v>
+      </c>
+      <c r="J11">
+        <v>1.81</v>
+      </c>
+      <c r="K11" s="1">
+        <v>678.75</v>
+      </c>
+      <c r="L11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12">
         <v>25.32</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12">
         <v>1.22</v>
       </c>
-      <c r="H11">
+      <c r="I12" s="1">
         <v>30.89</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J12">
         <v>1.22</v>
       </c>
-      <c r="J11">
+      <c r="K12" s="1">
         <v>30.89</v>
       </c>
-      <c r="K11" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>329553</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12">
-        <v>1198</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12">
-        <v>375</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="H12">
-        <v>607.5</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="J12">
-        <v>678.75</v>
-      </c>
-      <c r="K12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+      <c r="L12" t="s">
+        <v>60</v>
       </c>
       <c r="M12">
-        <v>329553</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13">
-        <v>1134</v>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F13">
         <v>189.24</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13">
         <v>1.62</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>306.57</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.78</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>336.85</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>179257</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14">
-        <v>1147</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F14">
         <v>105.67</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14">
         <v>1.62</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>171.19</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.78</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>188.09</v>
       </c>
-      <c r="K14" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
+      <c r="L14" t="s">
+        <v>62</v>
       </c>
       <c r="M14">
-        <v>180404</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15">
-        <v>1198</v>
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>275</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15">
+        <v>1.62</v>
+      </c>
+      <c r="I15" s="1">
+        <v>445.5</v>
+      </c>
+      <c r="J15">
+        <v>1.8</v>
+      </c>
+      <c r="K15" s="1">
+        <v>495</v>
+      </c>
+      <c r="L15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>23.75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16">
+        <v>1.22</v>
+      </c>
+      <c r="I16" s="1">
+        <v>28.98</v>
+      </c>
+      <c r="J16">
+        <v>1.22</v>
+      </c>
+      <c r="K16" s="1">
+        <v>28.98</v>
+      </c>
+      <c r="L16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
       </c>
-      <c r="F15">
-        <v>23.75</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="H15">
-        <v>28.98</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="J15">
-        <v>28.98</v>
-      </c>
-      <c r="K15" t="s">
-        <v>45</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>330178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16">
-        <v>1198</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16">
-        <v>275</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="H16">
-        <v>445.5</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J16">
-        <v>495</v>
-      </c>
-      <c r="K16" t="s">
-        <v>45</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>330178</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17">
-        <v>1147</v>
-      </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F17">
         <v>263.08</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17">
         <v>1.61</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>423.56</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.76</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>463.02</v>
       </c>
-      <c r="K17" t="s">
-        <v>46</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
+      <c r="L17" t="s">
+        <v>64</v>
       </c>
       <c r="M17">
-        <v>181467</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18">
-        <v>1164</v>
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F18">
         <v>228.66</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18">
         <v>1.61</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>368.14</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.76</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>402.44</v>
       </c>
-      <c r="K18" t="s">
-        <v>47</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
+      <c r="L18" t="s">
+        <v>65</v>
       </c>
       <c r="M18">
-        <v>85725</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19">
-        <v>1178</v>
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F19">
         <v>64.41</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19">
         <v>1.61</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>103.7</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.76</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>113.36</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20">
+        <v>106.18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20">
+        <v>1.61</v>
+      </c>
+      <c r="I20" s="1">
+        <v>170.95</v>
+      </c>
+      <c r="J20">
+        <v>1.75</v>
+      </c>
+      <c r="K20" s="1">
+        <v>185.82</v>
+      </c>
+      <c r="L20" t="s">
+        <v>67</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
         <v>48</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>107001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="4" t="s">
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21">
+        <v>277.8</v>
+      </c>
+      <c r="G21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21">
+        <v>1.59</v>
+      </c>
+      <c r="I21" s="1">
+        <v>441.7</v>
+      </c>
+      <c r="J21">
+        <v>1.75</v>
+      </c>
+      <c r="K21" s="1">
+        <v>486.15</v>
+      </c>
+      <c r="L21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22">
+        <v>200</v>
+      </c>
+      <c r="G22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22">
+        <v>1.59</v>
+      </c>
+      <c r="I22" s="1">
+        <v>318</v>
+      </c>
+      <c r="J22">
+        <v>1.75</v>
+      </c>
+      <c r="K22" s="1">
+        <v>350</v>
+      </c>
+      <c r="L22" t="s">
+        <v>69</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23">
+        <v>175</v>
+      </c>
+      <c r="G23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23">
+        <v>1.59</v>
+      </c>
+      <c r="I23" s="1">
+        <v>278.25</v>
+      </c>
+      <c r="J23">
+        <v>1.77</v>
+      </c>
+      <c r="K23" s="1">
+        <v>309.75</v>
+      </c>
+      <c r="L23" t="s">
+        <v>70</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="6">
-        <v>2844.28</v>
-      </c>
-      <c r="C24" s="6">
-        <v>15</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1.6244</v>
-      </c>
-      <c r="E24" s="6">
-        <v>4620.18</v>
-      </c>
-      <c r="F24" s="6">
-        <v>5088.85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="5" t="s">
+      <c r="F24">
+        <v>19.87</v>
+      </c>
+      <c r="G24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24">
+        <v>1.22</v>
+      </c>
+      <c r="I24" s="1">
+        <v>24.24</v>
+      </c>
+      <c r="J24">
+        <v>1.22</v>
+      </c>
+      <c r="K24" s="1">
+        <v>24.24</v>
+      </c>
+      <c r="L24" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="6">
-        <v>75.09</v>
-      </c>
-      <c r="C25" s="6">
-        <v>3</v>
-      </c>
-      <c r="D25" s="7">
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25">
+        <v>254.44</v>
+      </c>
+      <c r="G25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25">
+        <v>1.59</v>
+      </c>
+      <c r="I25" s="1">
+        <v>404.56</v>
+      </c>
+      <c r="J25">
+        <v>1.75</v>
+      </c>
+      <c r="K25" s="1">
+        <v>445.27</v>
+      </c>
+      <c r="L25" t="s">
+        <v>71</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26">
+        <v>104.62</v>
+      </c>
+      <c r="G26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H26">
+        <v>1.59</v>
+      </c>
+      <c r="I26" s="1">
+        <v>166.35</v>
+      </c>
+      <c r="J26">
+        <v>1.75</v>
+      </c>
+      <c r="K26" s="1">
+        <v>183.08</v>
+      </c>
+      <c r="L26" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27">
+        <v>180</v>
+      </c>
+      <c r="G27" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27">
+        <v>1.59</v>
+      </c>
+      <c r="I27" s="1">
+        <v>286.2</v>
+      </c>
+      <c r="J27">
+        <v>1.74</v>
+      </c>
+      <c r="K27" s="1">
+        <v>313.2</v>
+      </c>
+      <c r="L27" t="s">
+        <v>73</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28">
+        <v>455</v>
+      </c>
+      <c r="G28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28">
+        <v>1.59</v>
+      </c>
+      <c r="I28" s="1">
+        <v>723.45</v>
+      </c>
+      <c r="J28">
+        <v>1.74</v>
+      </c>
+      <c r="K28" s="1">
+        <v>791.7</v>
+      </c>
+      <c r="L28" t="s">
+        <v>74</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29">
+        <v>58.73</v>
+      </c>
+      <c r="G29" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29">
+        <v>1.59</v>
+      </c>
+      <c r="I29" s="1">
+        <v>93.38</v>
+      </c>
+      <c r="J29">
+        <v>1.74</v>
+      </c>
+      <c r="K29" s="1">
+        <v>102.19</v>
+      </c>
+      <c r="L29" t="s">
+        <v>75</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30">
+        <v>132.19</v>
+      </c>
+      <c r="G30" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30">
+        <v>1.59</v>
+      </c>
+      <c r="I30" s="1">
+        <v>210.18</v>
+      </c>
+      <c r="J30">
+        <v>1.72</v>
+      </c>
+      <c r="K30" s="1">
+        <v>227.37</v>
+      </c>
+      <c r="L30" t="s">
+        <v>76</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31">
+        <v>253.44</v>
+      </c>
+      <c r="G31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31">
+        <v>1.59</v>
+      </c>
+      <c r="I31" s="1">
+        <v>402.97</v>
+      </c>
+      <c r="J31">
+        <v>1.72</v>
+      </c>
+      <c r="K31" s="1">
+        <v>435.92</v>
+      </c>
+      <c r="L31" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32">
+        <v>175</v>
+      </c>
+      <c r="G32" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32">
+        <v>1.59</v>
+      </c>
+      <c r="I32" s="1">
+        <v>278.25</v>
+      </c>
+      <c r="J32">
+        <v>1.72</v>
+      </c>
+      <c r="K32" s="1">
+        <v>301</v>
+      </c>
+      <c r="L32" t="s">
+        <v>78</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33">
+        <v>217.11</v>
+      </c>
+      <c r="G33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33">
+        <v>1.59</v>
+      </c>
+      <c r="I33" s="1">
+        <v>345.2</v>
+      </c>
+      <c r="J33">
+        <v>1.71</v>
+      </c>
+      <c r="K33" s="1">
+        <v>371.26</v>
+      </c>
+      <c r="L33" t="s">
+        <v>79</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34">
+        <v>50</v>
+      </c>
+      <c r="G34" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34">
+        <v>1.58</v>
+      </c>
+      <c r="I34" s="1">
+        <v>79</v>
+      </c>
+      <c r="J34">
+        <v>1.69</v>
+      </c>
+      <c r="K34" s="1">
+        <v>84.5</v>
+      </c>
+      <c r="L34" t="s">
+        <v>80</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="6">
+        <v>5483.79</v>
+      </c>
+      <c r="C39" s="6">
+        <v>29</v>
+      </c>
+      <c r="D39" s="7">
+        <v>1.6081</v>
+      </c>
+      <c r="E39" s="6">
+        <v>8818.620000000001</v>
+      </c>
+      <c r="F39" s="6">
+        <v>9676.059999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="6">
+        <v>94.95999999999999</v>
+      </c>
+      <c r="C40" s="6">
+        <v>4</v>
+      </c>
+      <c r="D40" s="7">
         <v>1.22</v>
       </c>
-      <c r="E25" s="6">
-        <v>91.61</v>
-      </c>
-      <c r="F25" s="6">
-        <v>91.61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="9">
-        <v>2919.37</v>
-      </c>
-      <c r="C26" s="9">
-        <v>18</v>
-      </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="9">
-        <v>4711.79</v>
-      </c>
-      <c r="F26" s="9">
-        <v>5180.46</v>
+      <c r="E40" s="6">
+        <v>115.85</v>
+      </c>
+      <c r="F40" s="6">
+        <v>115.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="9">
+        <v>5578.75</v>
+      </c>
+      <c r="C41" s="9">
+        <v>33</v>
+      </c>
+      <c r="D41" s="7"/>
+      <c r="E41" s="9">
+        <v>8934.469999999999</v>
+      </c>
+      <c r="F41" s="9">
+        <v>9791.91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
@@ -397,7 +397,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,12 +407,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,17 +456,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="134">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-02</t>
   </si>
   <si>
@@ -82,19 +88,55 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Русе Дружба</t>
-  </si>
-  <si>
-    <t>Русе България</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Бургас езеро</t>
-  </si>
-  <si>
-    <t>Тракия Езеро</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1172 Русе Шелф</t>
+  </si>
+  <si>
+    <t>1178 Русе, бул. България</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1133 Кресна Е 79</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
   </si>
   <si>
     <t>Р7826КН</t>
@@ -112,6 +154,9 @@
     <t>Р2948КН</t>
   </si>
   <si>
+    <t>СВ0305ТТ</t>
+  </si>
+  <si>
     <t>78970110027720183</t>
   </si>
   <si>
@@ -127,79 +172,232 @@
     <t>78970110027720167</t>
   </si>
   <si>
+    <t>78970110027720209</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>ADBLUE 1L</t>
   </si>
   <si>
-    <t>2026-07-02 10:04:52</t>
-  </si>
-  <si>
-    <t>2026-07-02 11:44:00</t>
-  </si>
-  <si>
-    <t>2026-07-03 00:18:19</t>
-  </si>
-  <si>
-    <t>2026-07-03 10:17:23</t>
-  </si>
-  <si>
-    <t>2026-07-03 11:19:13</t>
-  </si>
-  <si>
-    <t>2026-07-06 09:16:40</t>
-  </si>
-  <si>
-    <t>2026-07-06 17:28:41</t>
-  </si>
-  <si>
-    <t>2026-07-06 20:26:51</t>
-  </si>
-  <si>
-    <t>2026-07-06 20:26:52</t>
-  </si>
-  <si>
-    <t>2026-07-07 16:34:55</t>
-  </si>
-  <si>
-    <t>2026-07-07 17:11:33</t>
-  </si>
-  <si>
-    <t>2026-07-08 09:43:23</t>
-  </si>
-  <si>
-    <t>2026-07-08 10:29:59</t>
-  </si>
-  <si>
-    <t>2026-07-08 10:58:14</t>
-  </si>
-  <si>
-    <t>2026-07-09 17:30:42</t>
-  </si>
-  <si>
-    <t>2026-07-10 17:12:34</t>
-  </si>
-  <si>
-    <t>2026-07-13 12:42:06</t>
-  </si>
-  <si>
-    <t>2026-07-14 14:56:37</t>
-  </si>
-  <si>
-    <t>2026-07-14 16:27:06</t>
-  </si>
-  <si>
-    <t>2026-07-14 16:58:50</t>
-  </si>
-  <si>
-    <t>2026-07-14 19:31:02</t>
-  </si>
-  <si>
-    <t>2026-07-14 19:31:03</t>
-  </si>
-  <si>
-    <t>2026-07-15 14:47:18</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:04:00</t>
+  </si>
+  <si>
+    <t>11:44:00</t>
+  </si>
+  <si>
+    <t>00:18:00</t>
+  </si>
+  <si>
+    <t>11:19:00</t>
+  </si>
+  <si>
+    <t>10:17:00</t>
+  </si>
+  <si>
+    <t>09:16:00</t>
+  </si>
+  <si>
+    <t>17:28:00</t>
+  </si>
+  <si>
+    <t>20:26:00</t>
+  </si>
+  <si>
+    <t>16:34:00</t>
+  </si>
+  <si>
+    <t>17:11:00</t>
+  </si>
+  <si>
+    <t>09:43:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>10:56:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>17:12:00</t>
+  </si>
+  <si>
+    <t>12:41:00</t>
+  </si>
+  <si>
+    <t>14:56:00</t>
+  </si>
+  <si>
+    <t>19:30:00</t>
+  </si>
+  <si>
+    <t>16:27:00</t>
+  </si>
+  <si>
+    <t>16:58:00</t>
+  </si>
+  <si>
+    <t>14:48:00</t>
+  </si>
+  <si>
+    <t>17:08:00</t>
+  </si>
+  <si>
+    <t>20:42:00</t>
+  </si>
+  <si>
+    <t>17:42:00</t>
+  </si>
+  <si>
+    <t>13:50:00</t>
+  </si>
+  <si>
+    <t>15:54:00</t>
+  </si>
+  <si>
+    <t>13:01:00</t>
+  </si>
+  <si>
+    <t>17:33:00</t>
+  </si>
+  <si>
+    <t>16:16:00</t>
+  </si>
+  <si>
+    <t>18:17:00</t>
+  </si>
+  <si>
+    <t>21:49:00</t>
+  </si>
+  <si>
+    <t>16:35:00</t>
+  </si>
+  <si>
+    <t>18:19:00</t>
+  </si>
+  <si>
+    <t>18:55:00</t>
+  </si>
+  <si>
+    <t>16:07:00</t>
+  </si>
+  <si>
+    <t>19:34:00</t>
+  </si>
+  <si>
+    <t>3234205395 3234205395</t>
+  </si>
+  <si>
+    <t>3234196649 3234196649</t>
+  </si>
+  <si>
+    <t>3234232065 3234232065</t>
+  </si>
+  <si>
+    <t>3234258994 3234258994</t>
+  </si>
+  <si>
+    <t>3234261712 3234261712</t>
+  </si>
+  <si>
+    <t>3234383768 3234383768</t>
+  </si>
+  <si>
+    <t>3234400371 3234400371</t>
+  </si>
+  <si>
+    <t>3234411201 3234411201</t>
+  </si>
+  <si>
+    <t>3234448645 3234448645</t>
+  </si>
+  <si>
+    <t>3234456006 3234456006</t>
+  </si>
+  <si>
+    <t>3234467056 3234467056</t>
+  </si>
+  <si>
+    <t>3234481142 3234481142</t>
+  </si>
+  <si>
+    <t>3234470136 3234470136</t>
+  </si>
+  <si>
+    <t>3234545854 3234545854</t>
+  </si>
+  <si>
+    <t>3234642131 3234642131</t>
+  </si>
+  <si>
+    <t>3234751204 3234751204</t>
+  </si>
+  <si>
+    <t>3234787580 3234787580</t>
+  </si>
+  <si>
+    <t>3234765083 3234765083</t>
+  </si>
+  <si>
+    <t>3234773996 3234773996</t>
+  </si>
+  <si>
+    <t>3234800779 3234800779</t>
+  </si>
+  <si>
+    <t>3234841875 3234841875</t>
+  </si>
+  <si>
+    <t>3234960607 3234960607</t>
+  </si>
+  <si>
+    <t>3234962135 3234962135</t>
+  </si>
+  <si>
+    <t>3235056974 3235056974</t>
+  </si>
+  <si>
+    <t>3235153248 3235153248</t>
+  </si>
+  <si>
+    <t>3235202343 3235202343</t>
+  </si>
+  <si>
+    <t>3235234471 3235234471</t>
+  </si>
+  <si>
+    <t>3235308624 3235308624</t>
+  </si>
+  <si>
+    <t>3235441418 3235441418</t>
+  </si>
+  <si>
+    <t>3235452614 3235452614</t>
+  </si>
+  <si>
+    <t>3235499602 3235499602</t>
+  </si>
+  <si>
+    <t>3235496652 3235496652</t>
+  </si>
+  <si>
+    <t>3235543826 3235543826</t>
+  </si>
+  <si>
+    <t>3235594833 3235594833</t>
+  </si>
+  <si>
+    <t>3235648791 3235648791</t>
+  </si>
+  <si>
+    <t>3235663435 3235663435</t>
   </si>
   <si>
     <t>Общи литри по продукт / ЕВРОУЕЙ СЪРВИЗ ООД</t>
@@ -617,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -626,15 +824,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -671,972 +871,1908 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>150</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2">
         <v>1.4</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>210</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>226.5</v>
       </c>
-      <c r="K2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F3">
         <v>44.83</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3">
         <v>1.4</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>62.76</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>67.69</v>
       </c>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F4">
         <v>244</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4">
         <v>1.4</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>341.6</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.51</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>368.44</v>
       </c>
-      <c r="K4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5">
+        <v>179.14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5">
+        <v>1.4</v>
+      </c>
+      <c r="I5" s="1">
+        <v>250.8</v>
+      </c>
+      <c r="J5">
+        <v>1.51</v>
+      </c>
+      <c r="K5" s="1">
+        <v>270.5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
         <v>35</v>
       </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5">
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6">
         <v>386</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6">
         <v>1.4</v>
       </c>
-      <c r="H5">
+      <c r="I6" s="1">
         <v>540.4</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J6">
         <v>1.51</v>
       </c>
-      <c r="J5">
+      <c r="K6" s="1">
         <v>582.86</v>
       </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6">
-        <v>179.14</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="H6">
-        <v>250.8</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J6">
-        <v>270.5</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>43</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F7">
         <v>245.98</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7">
         <v>1.41</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>346.83</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.52</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>373.89</v>
       </c>
-      <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F8">
         <v>180</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8">
         <v>1.41</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>253.8</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.52</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>273.6</v>
       </c>
-      <c r="K8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="L8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F9">
         <v>215</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9">
         <v>1.41</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>303.15</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.52</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>326.8</v>
       </c>
-      <c r="K9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F10">
         <v>25.77</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10">
         <v>1.22</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>31.44</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.22</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>31.44</v>
       </c>
-      <c r="K10" t="s">
-        <v>47</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="L10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F11">
         <v>193.41</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11">
         <v>1.41</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>272.71</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.53</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>295.92</v>
       </c>
-      <c r="K11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="L11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F12">
         <v>185</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12">
         <v>1.41</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>260.85</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.52</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>281.2</v>
       </c>
-      <c r="K12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="L12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F13">
         <v>265</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13">
         <v>1.41</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>373.65</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.52</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>402.8</v>
       </c>
-      <c r="K13" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="L13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F14">
         <v>128.13</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14">
         <v>1.41</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>180.66</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.52</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>194.76</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
         <v>51</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>36</v>
-      </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F15">
         <v>410</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15">
         <v>1.41</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>578.1</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.56</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>639.6</v>
       </c>
-      <c r="K15" t="s">
-        <v>52</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="L15" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F16">
         <v>155.27</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16">
         <v>1.41</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>218.93</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.53</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>237.56</v>
       </c>
-      <c r="K16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="L16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F17">
         <v>110</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17">
         <v>1.44</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>158.4</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.54</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>169.4</v>
       </c>
-      <c r="K17" t="s">
-        <v>54</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="L17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F18">
         <v>214.52</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18">
         <v>1.45</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>311.05</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.56</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>334.65</v>
       </c>
-      <c r="K18" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="L18" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F19">
         <v>249.46</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19">
         <v>1.47</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>366.71</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.56</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>389.16</v>
       </c>
-      <c r="K19" t="s">
-        <v>56</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="L19" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20">
+        <v>345</v>
+      </c>
+      <c r="G20" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20">
+        <v>1.47</v>
+      </c>
+      <c r="I20" s="1">
+        <v>507.15</v>
+      </c>
+      <c r="J20">
+        <v>1.56</v>
+      </c>
+      <c r="K20" s="1">
+        <v>538.2</v>
+      </c>
+      <c r="L20" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21">
+        <v>25.26</v>
+      </c>
+      <c r="G21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21">
+        <v>1.22</v>
+      </c>
+      <c r="I21" s="1">
+        <v>30.82</v>
+      </c>
+      <c r="J21">
+        <v>1.22</v>
+      </c>
+      <c r="K21" s="1">
+        <v>30.82</v>
+      </c>
+      <c r="L21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22">
+        <v>210.02</v>
+      </c>
+      <c r="G22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22">
+        <v>1.47</v>
+      </c>
+      <c r="I22" s="1">
+        <v>308.73</v>
+      </c>
+      <c r="J22">
+        <v>1.56</v>
+      </c>
+      <c r="K22" s="1">
+        <v>327.63</v>
+      </c>
+      <c r="L22" t="s">
+        <v>74</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23">
+        <v>166.09</v>
+      </c>
+      <c r="G23" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23">
+        <v>1.47</v>
+      </c>
+      <c r="I23" s="1">
+        <v>244.15</v>
+      </c>
+      <c r="J23">
+        <v>1.56</v>
+      </c>
+      <c r="K23" s="1">
+        <v>259.1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>75</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="C20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20">
-        <v>210.02</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H20">
-        <v>308.73</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J20">
-        <v>327.63</v>
-      </c>
-      <c r="K20" t="s">
-        <v>57</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21">
-        <v>166.09</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H21">
-        <v>244.15</v>
-      </c>
-      <c r="I21" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J21">
-        <v>259.1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>58</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22">
-        <v>345</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H22">
-        <v>507.15</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J22">
-        <v>538.2</v>
-      </c>
-      <c r="K22" t="s">
-        <v>59</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23">
-        <v>25.26</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="H23">
-        <v>30.82</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="J23">
-        <v>30.82</v>
-      </c>
-      <c r="K23" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F24">
         <v>65</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24">
         <v>1.49</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="1">
         <v>96.84999999999999</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24">
         <v>1.58</v>
       </c>
-      <c r="J24">
+      <c r="K24" s="1">
         <v>102.7</v>
       </c>
-      <c r="K24" t="s">
-        <v>61</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:12">
-      <c r="A28" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6">
-        <v>4341.85</v>
-      </c>
-      <c r="C29" s="6">
-        <v>21</v>
-      </c>
-      <c r="D29" s="7">
-        <v>1.425</v>
-      </c>
-      <c r="E29" s="6">
-        <v>6187.28</v>
-      </c>
-      <c r="F29" s="6">
-        <v>6662.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6">
-        <v>51.03</v>
-      </c>
-      <c r="C30" s="6">
-        <v>2</v>
-      </c>
-      <c r="D30" s="7">
-        <v>1.2201</v>
-      </c>
-      <c r="E30" s="6">
-        <v>62.26</v>
-      </c>
-      <c r="F30" s="6">
-        <v>62.26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="A31" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="9">
-        <v>4392.88</v>
-      </c>
-      <c r="C31" s="9">
-        <v>23</v>
-      </c>
-      <c r="D31" s="7"/>
-      <c r="E31" s="9">
-        <v>6249.54</v>
-      </c>
-      <c r="F31" s="9">
-        <v>6725.22</v>
+      <c r="L24" t="s">
+        <v>76</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25">
+        <v>215</v>
+      </c>
+      <c r="G25" t="s">
+        <v>55</v>
+      </c>
+      <c r="H25">
+        <v>1.5</v>
+      </c>
+      <c r="I25" s="1">
+        <v>322.5</v>
+      </c>
+      <c r="J25">
+        <v>1.63</v>
+      </c>
+      <c r="K25" s="1">
+        <v>350.45</v>
+      </c>
+      <c r="L25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26">
+        <v>128.22</v>
+      </c>
+      <c r="G26" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26">
+        <v>1.5</v>
+      </c>
+      <c r="I26" s="1">
+        <v>192.33</v>
+      </c>
+      <c r="J26">
+        <v>1.63</v>
+      </c>
+      <c r="K26" s="1">
+        <v>209</v>
+      </c>
+      <c r="L26" t="s">
+        <v>78</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27">
+        <v>265.01</v>
+      </c>
+      <c r="G27" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27">
+        <v>1.53</v>
+      </c>
+      <c r="I27" s="1">
+        <v>405.47</v>
+      </c>
+      <c r="J27">
+        <v>1.68</v>
+      </c>
+      <c r="K27" s="1">
+        <v>445.22</v>
+      </c>
+      <c r="L27" t="s">
+        <v>79</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28">
+        <v>220.02</v>
+      </c>
+      <c r="G28" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28">
+        <v>1.59</v>
+      </c>
+      <c r="I28" s="1">
+        <v>349.83</v>
+      </c>
+      <c r="J28">
+        <v>1.69</v>
+      </c>
+      <c r="K28" s="1">
+        <v>371.83</v>
+      </c>
+      <c r="L28" t="s">
+        <v>80</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29">
+        <v>154.08</v>
+      </c>
+      <c r="G29" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29">
+        <v>1.59</v>
+      </c>
+      <c r="I29" s="1">
+        <v>244.99</v>
+      </c>
+      <c r="J29">
+        <v>1.69</v>
+      </c>
+      <c r="K29" s="1">
+        <v>260.4</v>
+      </c>
+      <c r="L29" t="s">
+        <v>81</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30">
+        <v>310</v>
+      </c>
+      <c r="G30" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30">
+        <v>1.59</v>
+      </c>
+      <c r="I30" s="1">
+        <v>492.9</v>
+      </c>
+      <c r="J30">
+        <v>1.7</v>
+      </c>
+      <c r="K30" s="1">
+        <v>527</v>
+      </c>
+      <c r="L30" t="s">
+        <v>82</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31">
+        <v>22.7</v>
+      </c>
+      <c r="G31" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31">
+        <v>1.22</v>
+      </c>
+      <c r="I31" s="1">
+        <v>27.69</v>
+      </c>
+      <c r="J31">
+        <v>1.22</v>
+      </c>
+      <c r="K31" s="1">
+        <v>27.69</v>
+      </c>
+      <c r="L31" t="s">
+        <v>82</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32">
+        <v>110.42</v>
+      </c>
+      <c r="G32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32">
+        <v>1.62</v>
+      </c>
+      <c r="I32" s="1">
+        <v>178.88</v>
+      </c>
+      <c r="J32">
+        <v>1.72</v>
+      </c>
+      <c r="K32" s="1">
+        <v>189.92</v>
+      </c>
+      <c r="L32" t="s">
+        <v>83</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33">
+        <v>270</v>
+      </c>
+      <c r="G33" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33">
+        <v>1.62</v>
+      </c>
+      <c r="I33" s="1">
+        <v>437.4</v>
+      </c>
+      <c r="J33">
+        <v>1.75</v>
+      </c>
+      <c r="K33" s="1">
+        <v>472.5</v>
+      </c>
+      <c r="L33" t="s">
+        <v>84</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34">
+        <v>22.08</v>
+      </c>
+      <c r="G34" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34">
+        <v>1.22</v>
+      </c>
+      <c r="I34" s="1">
+        <v>26.94</v>
+      </c>
+      <c r="J34">
+        <v>1.22</v>
+      </c>
+      <c r="K34" s="1">
+        <v>26.94</v>
+      </c>
+      <c r="L34" t="s">
+        <v>84</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35">
+        <v>180</v>
+      </c>
+      <c r="G35" t="s">
+        <v>55</v>
+      </c>
+      <c r="H35">
+        <v>1.62</v>
+      </c>
+      <c r="I35" s="1">
+        <v>291.6</v>
+      </c>
+      <c r="J35">
+        <v>1.75</v>
+      </c>
+      <c r="K35" s="1">
+        <v>315</v>
+      </c>
+      <c r="L35" t="s">
+        <v>85</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36">
+        <v>150</v>
+      </c>
+      <c r="G36" t="s">
+        <v>55</v>
+      </c>
+      <c r="H36">
+        <v>1.65</v>
+      </c>
+      <c r="I36" s="1">
+        <v>247.5</v>
+      </c>
+      <c r="J36">
+        <v>1.78</v>
+      </c>
+      <c r="K36" s="1">
+        <v>267</v>
+      </c>
+      <c r="L36" t="s">
+        <v>86</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37">
+        <v>150.04</v>
+      </c>
+      <c r="G37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37">
+        <v>1.65</v>
+      </c>
+      <c r="I37" s="1">
+        <v>247.57</v>
+      </c>
+      <c r="J37">
+        <v>1.75</v>
+      </c>
+      <c r="K37" s="1">
+        <v>262.57</v>
+      </c>
+      <c r="L37" t="s">
+        <v>87</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" t="s">
+        <v>53</v>
+      </c>
+      <c r="F38">
+        <v>210</v>
+      </c>
+      <c r="G38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38">
+        <v>1.67</v>
+      </c>
+      <c r="I38" s="1">
+        <v>350.7</v>
+      </c>
+      <c r="J38">
+        <v>1.75</v>
+      </c>
+      <c r="K38" s="1">
+        <v>367.5</v>
+      </c>
+      <c r="L38" t="s">
+        <v>88</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39">
+        <v>100</v>
+      </c>
+      <c r="G39" t="s">
+        <v>55</v>
+      </c>
+      <c r="H39">
+        <v>1.67</v>
+      </c>
+      <c r="I39" s="1">
+        <v>167</v>
+      </c>
+      <c r="J39">
+        <v>1.79</v>
+      </c>
+      <c r="K39" s="1">
+        <v>179</v>
+      </c>
+      <c r="L39" t="s">
+        <v>89</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40">
+        <v>225.01</v>
+      </c>
+      <c r="G40" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40">
+        <v>1.69</v>
+      </c>
+      <c r="I40" s="1">
+        <v>380.27</v>
+      </c>
+      <c r="J40">
+        <v>1.78</v>
+      </c>
+      <c r="K40" s="1">
+        <v>400.52</v>
+      </c>
+      <c r="L40" t="s">
+        <v>90</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41">
+        <v>26.52</v>
+      </c>
+      <c r="G41" t="s">
+        <v>55</v>
+      </c>
+      <c r="H41">
+        <v>1.22</v>
+      </c>
+      <c r="I41" s="1">
+        <v>32.35</v>
+      </c>
+      <c r="J41">
+        <v>1.22</v>
+      </c>
+      <c r="K41" s="1">
+        <v>32.35</v>
+      </c>
+      <c r="L41" t="s">
+        <v>90</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42">
+        <v>118.05</v>
+      </c>
+      <c r="G42" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42">
+        <v>1.69</v>
+      </c>
+      <c r="I42" s="1">
+        <v>199.5</v>
+      </c>
+      <c r="J42">
+        <v>1.78</v>
+      </c>
+      <c r="K42" s="1">
+        <v>210.13</v>
+      </c>
+      <c r="L42" t="s">
+        <v>91</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="6">
+        <v>7147.7</v>
+      </c>
+      <c r="C47" s="6">
+        <v>36</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1.4964</v>
+      </c>
+      <c r="E47" s="6">
+        <v>10695.72</v>
+      </c>
+      <c r="F47" s="6">
+        <v>11491</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="6">
+        <v>122.33</v>
+      </c>
+      <c r="C48" s="6">
+        <v>5</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1.22</v>
+      </c>
+      <c r="E48" s="6">
+        <v>149.24</v>
+      </c>
+      <c r="F48" s="6">
+        <v>149.24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B49" s="9">
+        <v>7270.03</v>
+      </c>
+      <c r="C49" s="9">
+        <v>41</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="9">
+        <v>10844.96</v>
+      </c>
+      <c r="F49" s="9">
+        <v>11640.24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A45:F45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
@@ -424,7 +424,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -2723,7 +2723,7 @@
         <v>36</v>
       </c>
       <c r="D47" s="7">
-        <v>1.4964</v>
+        <v>1.496386</v>
       </c>
       <c r="E47" s="6">
         <v>10695.72</v>
@@ -2743,7 +2743,7 @@
         <v>5</v>
       </c>
       <c r="D48" s="7">
-        <v>1.22</v>
+        <v>1.219979</v>
       </c>
       <c r="E48" s="6">
         <v>149.24</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="135">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -815,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -828,13 +831,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -877,1814 +880,1940 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2">
         <v>150</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>210</v>
+        <v>1.399</v>
       </c>
       <c r="J2">
+        <v>209.85</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>226.5</v>
       </c>
-      <c r="L2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="M2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3">
-        <v>44.83</v>
+        <v>44.828</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3">
-        <v>1.4</v>
+        <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>62.76</v>
+        <v>1.399</v>
       </c>
       <c r="J3">
+        <v>62.714372</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.51</v>
       </c>
-      <c r="K3" s="1">
-        <v>67.69</v>
-      </c>
-      <c r="L3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="L3" s="1">
+        <v>67.69028</v>
+      </c>
+      <c r="M3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4">
         <v>244</v>
       </c>
       <c r="G4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>1.399</v>
       </c>
       <c r="I4" s="1">
-        <v>341.6</v>
+        <v>1.399</v>
       </c>
       <c r="J4">
+        <v>341.356</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.51</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>368.44</v>
       </c>
-      <c r="L4" t="s">
-        <v>58</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="M4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F5">
-        <v>179.14</v>
+        <v>179.139</v>
       </c>
       <c r="G5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H5">
-        <v>1.4</v>
+        <v>1.399</v>
       </c>
       <c r="I5" s="1">
-        <v>250.8</v>
+        <v>1.399</v>
       </c>
       <c r="J5">
+        <v>250.615461</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.51</v>
       </c>
-      <c r="K5" s="1">
-        <v>270.5</v>
-      </c>
-      <c r="L5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="L5" s="1">
+        <v>270.49989</v>
+      </c>
+      <c r="M5" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6">
         <v>386</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6">
-        <v>1.4</v>
+        <v>1.399</v>
       </c>
       <c r="I6" s="1">
-        <v>540.4</v>
+        <v>1.399</v>
       </c>
       <c r="J6">
+        <v>540.014</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.51</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>582.86</v>
       </c>
-      <c r="L6" t="s">
-        <v>60</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="M6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7">
         <v>245.98</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H7">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I7" s="1">
-        <v>346.83</v>
+        <v>1.406</v>
       </c>
       <c r="J7">
+        <v>345.84788</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.52</v>
       </c>
-      <c r="K7" s="1">
-        <v>373.89</v>
-      </c>
-      <c r="L7" t="s">
-        <v>61</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="L7" s="1">
+        <v>373.8896</v>
+      </c>
+      <c r="M7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F8">
         <v>180</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H8">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I8" s="1">
-        <v>253.8</v>
+        <v>1.406</v>
       </c>
       <c r="J8">
+        <v>253.08</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.52</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>273.6</v>
       </c>
-      <c r="L8" t="s">
-        <v>62</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="M8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F9">
         <v>215</v>
       </c>
       <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9">
+        <v>1.406</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.406</v>
+      </c>
+      <c r="J9">
+        <v>302.29</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L9" s="1">
+        <v>326.8</v>
+      </c>
+      <c r="M9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
         <v>55</v>
-      </c>
-      <c r="H9">
-        <v>1.41</v>
-      </c>
-      <c r="I9" s="1">
-        <v>303.15</v>
-      </c>
-      <c r="J9">
-        <v>1.52</v>
-      </c>
-      <c r="K9" s="1">
-        <v>326.8</v>
-      </c>
-      <c r="L9" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>54</v>
       </c>
       <c r="F10">
         <v>25.77</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H10">
         <v>1.22</v>
       </c>
       <c r="I10" s="1">
-        <v>31.44</v>
+        <v>1.22</v>
       </c>
       <c r="J10">
+        <v>31.4394</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.22</v>
       </c>
-      <c r="K10" s="1">
-        <v>31.44</v>
-      </c>
-      <c r="L10" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="1">
+        <v>31.4394</v>
+      </c>
+      <c r="M10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11">
-        <v>193.41</v>
+        <v>193.412</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I11" s="1">
-        <v>272.71</v>
+        <v>1.406</v>
       </c>
       <c r="J11">
+        <v>271.937272</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.53</v>
       </c>
-      <c r="K11" s="1">
-        <v>295.92</v>
-      </c>
-      <c r="L11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="L11" s="1">
+        <v>295.92036</v>
+      </c>
+      <c r="M11" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12">
         <v>185</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12">
-        <v>1.41</v>
+        <v>1.406</v>
       </c>
       <c r="I12" s="1">
-        <v>260.85</v>
+        <v>1.406</v>
       </c>
       <c r="J12">
+        <v>260.11</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.52</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>281.2</v>
       </c>
-      <c r="L12" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="M12" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F13">
         <v>265</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13">
-        <v>1.41</v>
+        <v>1.412</v>
       </c>
       <c r="I13" s="1">
-        <v>373.65</v>
+        <v>1.412</v>
       </c>
       <c r="J13">
+        <v>374.18</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.52</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>402.8</v>
       </c>
-      <c r="L13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="M13" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14">
-        <v>128.13</v>
+        <v>128.132</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H14">
-        <v>1.41</v>
+        <v>1.412</v>
       </c>
       <c r="I14" s="1">
-        <v>180.66</v>
+        <v>1.412</v>
       </c>
       <c r="J14">
+        <v>180.922384</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.52</v>
       </c>
-      <c r="K14" s="1">
-        <v>194.76</v>
-      </c>
-      <c r="L14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="L14" s="1">
+        <v>194.76064</v>
+      </c>
+      <c r="M14" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15">
         <v>410</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15">
-        <v>1.41</v>
+        <v>1.412</v>
       </c>
       <c r="I15" s="1">
-        <v>578.1</v>
+        <v>1.412</v>
       </c>
       <c r="J15">
+        <v>578.92</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.56</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>639.6</v>
       </c>
-      <c r="L15" t="s">
-        <v>68</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="M15" t="s">
+        <v>69</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16">
+        <v>155.268</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16">
+        <v>1.412</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.412</v>
+      </c>
+      <c r="J16">
+        <v>219.238416</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="L16" s="1">
+        <v>237.56004</v>
+      </c>
+      <c r="M16" t="s">
+        <v>70</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>48</v>
       </c>
-      <c r="E16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16">
-        <v>155.27</v>
-      </c>
-      <c r="G16" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16">
-        <v>1.41</v>
-      </c>
-      <c r="I16" s="1">
-        <v>218.93</v>
-      </c>
-      <c r="J16">
-        <v>1.53</v>
-      </c>
-      <c r="K16" s="1">
-        <v>237.56</v>
-      </c>
-      <c r="L16" t="s">
-        <v>69</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>47</v>
-      </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F17">
         <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17">
-        <v>1.44</v>
+        <v>1.437</v>
       </c>
       <c r="I17" s="1">
-        <v>158.4</v>
+        <v>1.437</v>
       </c>
       <c r="J17">
+        <v>158.07</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.54</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>169.4</v>
       </c>
-      <c r="L17" t="s">
-        <v>70</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="M17" t="s">
+        <v>71</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18">
-        <v>214.52</v>
+        <v>214.519</v>
       </c>
       <c r="G18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H18">
-        <v>1.45</v>
+        <v>1.451</v>
       </c>
       <c r="I18" s="1">
-        <v>311.05</v>
+        <v>1.451</v>
       </c>
       <c r="J18">
+        <v>311.267069</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.56</v>
       </c>
-      <c r="K18" s="1">
-        <v>334.65</v>
-      </c>
-      <c r="L18" t="s">
-        <v>71</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="L18" s="1">
+        <v>334.64964</v>
+      </c>
+      <c r="M18" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19">
+        <v>249.462</v>
+      </c>
+      <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19">
+        <v>1.469</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1.469</v>
+      </c>
+      <c r="J19">
+        <v>366.459678</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L19" s="1">
+        <v>389.16072</v>
+      </c>
+      <c r="M19" t="s">
+        <v>73</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
         <v>36</v>
       </c>
-      <c r="C19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19">
-        <v>249.46</v>
-      </c>
-      <c r="G19" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19">
-        <v>1.47</v>
-      </c>
-      <c r="I19" s="1">
-        <v>366.71</v>
-      </c>
-      <c r="J19">
-        <v>1.56</v>
-      </c>
-      <c r="K19" s="1">
-        <v>389.16</v>
-      </c>
-      <c r="L19" t="s">
-        <v>72</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20">
         <v>345</v>
       </c>
       <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20">
+        <v>1.469</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1.469</v>
+      </c>
+      <c r="J20">
+        <v>506.805</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L20" s="1">
+        <v>538.2</v>
+      </c>
+      <c r="M20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" t="s">
         <v>55</v>
       </c>
-      <c r="H20">
-        <v>1.47</v>
-      </c>
-      <c r="I20" s="1">
-        <v>507.15</v>
-      </c>
-      <c r="J20">
-        <v>1.56</v>
-      </c>
-      <c r="K20" s="1">
-        <v>538.2</v>
-      </c>
-      <c r="L20" t="s">
-        <v>73</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" t="s">
-        <v>54</v>
-      </c>
       <c r="F21">
-        <v>25.26</v>
+        <v>25.262</v>
       </c>
       <c r="G21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H21">
         <v>1.22</v>
       </c>
       <c r="I21" s="1">
-        <v>30.82</v>
+        <v>1.22</v>
       </c>
       <c r="J21">
+        <v>30.81964</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.22</v>
       </c>
-      <c r="K21" s="1">
-        <v>30.82</v>
-      </c>
-      <c r="L21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="L21" s="1">
+        <v>30.81964</v>
+      </c>
+      <c r="M21" t="s">
+        <v>74</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22">
-        <v>210.02</v>
+        <v>210.019</v>
       </c>
       <c r="G22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H22">
-        <v>1.47</v>
+        <v>1.469</v>
       </c>
       <c r="I22" s="1">
-        <v>308.73</v>
+        <v>1.469</v>
       </c>
       <c r="J22">
+        <v>308.517911</v>
+      </c>
+      <c r="K22" s="1">
         <v>1.56</v>
       </c>
-      <c r="K22" s="1">
-        <v>327.63</v>
-      </c>
-      <c r="L22" t="s">
-        <v>74</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="L22" s="1">
+        <v>327.62964</v>
+      </c>
+      <c r="M22" t="s">
+        <v>75</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F23">
         <v>166.09</v>
       </c>
       <c r="G23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H23">
-        <v>1.47</v>
+        <v>1.469</v>
       </c>
       <c r="I23" s="1">
-        <v>244.15</v>
+        <v>1.469</v>
       </c>
       <c r="J23">
+        <v>243.98621</v>
+      </c>
+      <c r="K23" s="1">
         <v>1.56</v>
       </c>
-      <c r="K23" s="1">
-        <v>259.1</v>
-      </c>
-      <c r="L23" t="s">
-        <v>75</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="L23" s="1">
+        <v>259.1004</v>
+      </c>
+      <c r="M23" t="s">
+        <v>76</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F24">
         <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H24">
-        <v>1.49</v>
+        <v>1.489</v>
       </c>
       <c r="I24" s="1">
-        <v>96.84999999999999</v>
+        <v>1.489</v>
       </c>
       <c r="J24">
+        <v>96.785</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.58</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>102.7</v>
       </c>
-      <c r="L24" t="s">
-        <v>76</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="M24" t="s">
+        <v>77</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F25">
         <v>215</v>
       </c>
       <c r="G25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H25">
-        <v>1.5</v>
+        <v>1.499</v>
       </c>
       <c r="I25" s="1">
-        <v>322.5</v>
+        <v>1.499</v>
       </c>
       <c r="J25">
+        <v>322.285</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.63</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>350.45</v>
       </c>
-      <c r="L25" t="s">
-        <v>77</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="M25" t="s">
+        <v>78</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26">
+        <v>128.221</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26">
+        <v>1.499</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1.499</v>
+      </c>
+      <c r="J26">
+        <v>192.203279</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="L26" s="1">
+        <v>209.00023</v>
+      </c>
+      <c r="M26" t="s">
+        <v>79</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27">
+        <v>265.012</v>
+      </c>
+      <c r="G27" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27">
+        <v>1.528</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1.528</v>
+      </c>
+      <c r="J27">
+        <v>404.938336</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L27" s="1">
+        <v>445.22016</v>
+      </c>
+      <c r="M27" t="s">
+        <v>80</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
         <v>42</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D28" t="s">
         <v>48</v>
       </c>
-      <c r="E26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26">
-        <v>128.22</v>
-      </c>
-      <c r="G26" t="s">
-        <v>55</v>
-      </c>
-      <c r="H26">
-        <v>1.5</v>
-      </c>
-      <c r="I26" s="1">
-        <v>192.33</v>
-      </c>
-      <c r="J26">
-        <v>1.63</v>
-      </c>
-      <c r="K26" s="1">
-        <v>209</v>
-      </c>
-      <c r="L26" t="s">
-        <v>78</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27">
-        <v>265.01</v>
-      </c>
-      <c r="G27" t="s">
-        <v>55</v>
-      </c>
-      <c r="H27">
-        <v>1.53</v>
-      </c>
-      <c r="I27" s="1">
-        <v>405.47</v>
-      </c>
-      <c r="J27">
-        <v>1.68</v>
-      </c>
-      <c r="K27" s="1">
-        <v>445.22</v>
-      </c>
-      <c r="L27" t="s">
-        <v>79</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" t="s">
-        <v>47</v>
-      </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F28">
-        <v>220.02</v>
+        <v>220.018</v>
       </c>
       <c r="G28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H28">
-        <v>1.59</v>
+        <v>1.588</v>
       </c>
       <c r="I28" s="1">
-        <v>349.83</v>
+        <v>1.588</v>
       </c>
       <c r="J28">
+        <v>349.388584</v>
+      </c>
+      <c r="K28" s="1">
         <v>1.69</v>
       </c>
-      <c r="K28" s="1">
-        <v>371.83</v>
-      </c>
-      <c r="L28" t="s">
-        <v>80</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="L28" s="1">
+        <v>371.83042</v>
+      </c>
+      <c r="M28" t="s">
+        <v>81</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F29">
-        <v>154.08</v>
+        <v>154.083</v>
       </c>
       <c r="G29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H29">
-        <v>1.59</v>
+        <v>1.588</v>
       </c>
       <c r="I29" s="1">
-        <v>244.99</v>
+        <v>1.588</v>
       </c>
       <c r="J29">
+        <v>244.683804</v>
+      </c>
+      <c r="K29" s="1">
         <v>1.69</v>
       </c>
-      <c r="K29" s="1">
-        <v>260.4</v>
-      </c>
-      <c r="L29" t="s">
-        <v>81</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="L29" s="1">
+        <v>260.40027</v>
+      </c>
+      <c r="M29" t="s">
+        <v>82</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F30">
         <v>310</v>
       </c>
       <c r="G30" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30">
+        <v>1.588</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1.588</v>
+      </c>
+      <c r="J30">
+        <v>492.28</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L30" s="1">
+        <v>527</v>
+      </c>
+      <c r="M30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" t="s">
         <v>55</v>
       </c>
-      <c r="H30">
-        <v>1.59</v>
-      </c>
-      <c r="I30" s="1">
-        <v>492.9</v>
-      </c>
-      <c r="J30">
-        <v>1.7</v>
-      </c>
-      <c r="K30" s="1">
-        <v>527</v>
-      </c>
-      <c r="L30" t="s">
-        <v>82</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" t="s">
-        <v>54</v>
-      </c>
       <c r="F31">
-        <v>22.7</v>
+        <v>22.697</v>
       </c>
       <c r="G31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H31">
         <v>1.22</v>
       </c>
       <c r="I31" s="1">
-        <v>27.69</v>
+        <v>1.22</v>
       </c>
       <c r="J31">
+        <v>27.69034</v>
+      </c>
+      <c r="K31" s="1">
         <v>1.22</v>
       </c>
-      <c r="K31" s="1">
-        <v>27.69</v>
-      </c>
-      <c r="L31" t="s">
-        <v>82</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="L31" s="1">
+        <v>27.69034</v>
+      </c>
+      <c r="M31" t="s">
+        <v>83</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F32">
-        <v>110.42</v>
+        <v>110.419</v>
       </c>
       <c r="G32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H32">
-        <v>1.62</v>
+        <v>1.619</v>
       </c>
       <c r="I32" s="1">
-        <v>178.88</v>
+        <v>1.619</v>
       </c>
       <c r="J32">
+        <v>178.768361</v>
+      </c>
+      <c r="K32" s="1">
         <v>1.72</v>
       </c>
-      <c r="K32" s="1">
-        <v>189.92</v>
-      </c>
-      <c r="L32" t="s">
-        <v>83</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="L32" s="1">
+        <v>189.92068</v>
+      </c>
+      <c r="M32" t="s">
+        <v>84</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F33">
         <v>270</v>
       </c>
       <c r="G33" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33">
+        <v>1.619</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1.619</v>
+      </c>
+      <c r="J33">
+        <v>437.13</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L33" s="1">
+        <v>472.5</v>
+      </c>
+      <c r="M33" t="s">
+        <v>85</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" t="s">
         <v>55</v>
       </c>
-      <c r="H33">
-        <v>1.62</v>
-      </c>
-      <c r="I33" s="1">
-        <v>437.4</v>
-      </c>
-      <c r="J33">
-        <v>1.75</v>
-      </c>
-      <c r="K33" s="1">
-        <v>472.5</v>
-      </c>
-      <c r="L33" t="s">
-        <v>84</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" t="s">
-        <v>54</v>
-      </c>
       <c r="F34">
-        <v>22.08</v>
+        <v>22.082</v>
       </c>
       <c r="G34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H34">
         <v>1.22</v>
       </c>
       <c r="I34" s="1">
-        <v>26.94</v>
+        <v>1.22</v>
       </c>
       <c r="J34">
+        <v>26.94004</v>
+      </c>
+      <c r="K34" s="1">
         <v>1.22</v>
       </c>
-      <c r="K34" s="1">
-        <v>26.94</v>
-      </c>
-      <c r="L34" t="s">
-        <v>84</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="L34" s="1">
+        <v>26.94004</v>
+      </c>
+      <c r="M34" t="s">
+        <v>85</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F35">
         <v>180</v>
       </c>
       <c r="G35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H35">
-        <v>1.62</v>
+        <v>1.619</v>
       </c>
       <c r="I35" s="1">
-        <v>291.6</v>
+        <v>1.619</v>
       </c>
       <c r="J35">
+        <v>291.42</v>
+      </c>
+      <c r="K35" s="1">
         <v>1.75</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>315</v>
       </c>
-      <c r="L35" t="s">
-        <v>85</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="M35" t="s">
+        <v>86</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F36">
         <v>150</v>
       </c>
       <c r="G36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H36">
-        <v>1.65</v>
+        <v>1.653</v>
       </c>
       <c r="I36" s="1">
-        <v>247.5</v>
+        <v>1.653</v>
       </c>
       <c r="J36">
+        <v>247.95</v>
+      </c>
+      <c r="K36" s="1">
         <v>1.78</v>
       </c>
-      <c r="K36" s="1">
+      <c r="L36" s="1">
         <v>267</v>
       </c>
-      <c r="L36" t="s">
-        <v>86</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="M36" t="s">
+        <v>87</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F37">
         <v>150.04</v>
       </c>
       <c r="G37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H37">
-        <v>1.65</v>
+        <v>1.653</v>
       </c>
       <c r="I37" s="1">
-        <v>247.57</v>
+        <v>1.653</v>
       </c>
       <c r="J37">
+        <v>248.01612</v>
+      </c>
+      <c r="K37" s="1">
         <v>1.75</v>
       </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
         <v>262.57</v>
       </c>
-      <c r="L37" t="s">
-        <v>87</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="M37" t="s">
+        <v>88</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F38">
         <v>210</v>
       </c>
       <c r="G38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H38">
-        <v>1.67</v>
+        <v>1.674</v>
       </c>
       <c r="I38" s="1">
-        <v>350.7</v>
+        <v>1.674</v>
       </c>
       <c r="J38">
+        <v>351.54</v>
+      </c>
+      <c r="K38" s="1">
         <v>1.75</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>367.5</v>
       </c>
-      <c r="L38" t="s">
-        <v>88</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="M38" t="s">
+        <v>89</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F39">
         <v>100</v>
       </c>
       <c r="G39" t="s">
+        <v>56</v>
+      </c>
+      <c r="H39">
+        <v>1.674</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1.674</v>
+      </c>
+      <c r="J39">
+        <v>167.4</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="L39" s="1">
+        <v>179</v>
+      </c>
+      <c r="M39" t="s">
+        <v>90</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F40">
+        <v>225.011</v>
+      </c>
+      <c r="G40" t="s">
+        <v>56</v>
+      </c>
+      <c r="H40">
+        <v>1.689</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1.689</v>
+      </c>
+      <c r="J40">
+        <v>380.043579</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1.78</v>
+      </c>
+      <c r="L40" s="1">
+        <v>400.51958</v>
+      </c>
+      <c r="M40" t="s">
+        <v>91</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" t="s">
         <v>55</v>
       </c>
-      <c r="H39">
-        <v>1.67</v>
-      </c>
-      <c r="I39" s="1">
-        <v>167</v>
-      </c>
-      <c r="J39">
-        <v>1.79</v>
-      </c>
-      <c r="K39" s="1">
-        <v>179</v>
-      </c>
-      <c r="L39" t="s">
-        <v>89</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40">
-        <v>225.01</v>
-      </c>
-      <c r="G40" t="s">
-        <v>55</v>
-      </c>
-      <c r="H40">
-        <v>1.69</v>
-      </c>
-      <c r="I40" s="1">
-        <v>380.27</v>
-      </c>
-      <c r="J40">
-        <v>1.78</v>
-      </c>
-      <c r="K40" s="1">
-        <v>400.52</v>
-      </c>
-      <c r="L40" t="s">
-        <v>90</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" t="s">
-        <v>54</v>
-      </c>
       <c r="F41">
-        <v>26.52</v>
+        <v>26.516</v>
       </c>
       <c r="G41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H41">
         <v>1.22</v>
       </c>
       <c r="I41" s="1">
-        <v>32.35</v>
+        <v>1.22</v>
       </c>
       <c r="J41">
+        <v>32.34952</v>
+      </c>
+      <c r="K41" s="1">
         <v>1.22</v>
       </c>
-      <c r="K41" s="1">
-        <v>32.35</v>
-      </c>
-      <c r="L41" t="s">
-        <v>90</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="L41" s="1">
+        <v>32.34952</v>
+      </c>
+      <c r="M41" t="s">
+        <v>91</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F42">
-        <v>118.05</v>
+        <v>118.051</v>
       </c>
       <c r="G42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H42">
-        <v>1.69</v>
+        <v>1.689</v>
       </c>
       <c r="I42" s="1">
-        <v>199.5</v>
+        <v>1.689</v>
       </c>
       <c r="J42">
+        <v>199.388139</v>
+      </c>
+      <c r="K42" s="1">
         <v>1.78</v>
       </c>
-      <c r="K42" s="1">
-        <v>210.13</v>
-      </c>
-      <c r="L42" t="s">
-        <v>91</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="L42" s="1">
+        <v>210.13078</v>
+      </c>
+      <c r="M42" t="s">
+        <v>92</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2692,58 +2821,58 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:15">
       <c r="A46" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="6">
-        <v>7147.7</v>
+        <v>7147.704</v>
       </c>
       <c r="C47" s="6">
         <v>36</v>
       </c>
       <c r="D47" s="7">
-        <v>1.496386</v>
+        <v>1.495641</v>
       </c>
       <c r="E47" s="6">
-        <v>10695.72</v>
+        <v>10690.4</v>
       </c>
       <c r="F47" s="6">
         <v>11491</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:15">
       <c r="A48" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="6">
-        <v>122.33</v>
+        <v>122.327</v>
       </c>
       <c r="C48" s="6">
         <v>5</v>
       </c>
       <c r="D48" s="7">
-        <v>1.219979</v>
+        <v>1.22</v>
       </c>
       <c r="E48" s="6">
         <v>149.24</v>
@@ -2754,17 +2883,17 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B49" s="9">
-        <v>7270.03</v>
+        <v>7270.031</v>
       </c>
       <c r="C49" s="9">
         <v>41</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="9">
-        <v>10844.96</v>
+        <v>10839.64</v>
       </c>
       <c r="F49" s="9">
         <v>11640.24</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="134">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -426,8 +423,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -520,10 +517,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -818,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -831,13 +828,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -880,1940 +877,1814 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>150</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H2">
         <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>1.399</v>
+        <v>209.85</v>
       </c>
       <c r="J2">
-        <v>209.85</v>
+        <v>1.51</v>
       </c>
       <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
         <v>226.5</v>
       </c>
-      <c r="M2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="L2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3">
         <v>44.828</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H3">
         <v>1.399</v>
       </c>
       <c r="I3" s="1">
-        <v>1.399</v>
+        <v>62.714</v>
       </c>
       <c r="J3">
-        <v>62.714372</v>
+        <v>1.51</v>
       </c>
       <c r="K3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L3" s="1">
-        <v>67.69028</v>
-      </c>
-      <c r="M3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>67.69</v>
+      </c>
+      <c r="L3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F4">
         <v>244</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H4">
         <v>1.399</v>
       </c>
       <c r="I4" s="1">
-        <v>1.399</v>
+        <v>341.356</v>
       </c>
       <c r="J4">
-        <v>341.356</v>
+        <v>1.51</v>
       </c>
       <c r="K4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L4" s="1">
         <v>368.44</v>
       </c>
-      <c r="M4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="L4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F5">
         <v>179.139</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H5">
         <v>1.399</v>
       </c>
       <c r="I5" s="1">
-        <v>1.399</v>
+        <v>250.615</v>
       </c>
       <c r="J5">
-        <v>250.615461</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
-        <v>270.49989</v>
-      </c>
-      <c r="M5" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>270.5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6">
         <v>386</v>
       </c>
       <c r="G6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H6">
         <v>1.399</v>
       </c>
       <c r="I6" s="1">
-        <v>1.399</v>
+        <v>540.014</v>
       </c>
       <c r="J6">
-        <v>540.014</v>
+        <v>1.51</v>
       </c>
       <c r="K6" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L6" s="1">
         <v>582.86</v>
       </c>
-      <c r="M6" t="s">
-        <v>61</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="L6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F7">
         <v>245.98</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H7">
         <v>1.406</v>
       </c>
       <c r="I7" s="1">
-        <v>1.406</v>
+        <v>345.848</v>
       </c>
       <c r="J7">
-        <v>345.84788</v>
+        <v>1.52</v>
       </c>
       <c r="K7" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L7" s="1">
-        <v>373.8896</v>
-      </c>
-      <c r="M7" t="s">
-        <v>62</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>373.89</v>
+      </c>
+      <c r="L7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8">
         <v>180</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H8">
         <v>1.406</v>
       </c>
       <c r="I8" s="1">
-        <v>1.406</v>
+        <v>253.08</v>
       </c>
       <c r="J8">
-        <v>253.08</v>
+        <v>1.52</v>
       </c>
       <c r="K8" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L8" s="1">
         <v>273.6</v>
       </c>
-      <c r="M8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="L8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9">
         <v>215</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H9">
         <v>1.406</v>
       </c>
       <c r="I9" s="1">
-        <v>1.406</v>
+        <v>302.29</v>
       </c>
       <c r="J9">
-        <v>302.29</v>
+        <v>1.52</v>
       </c>
       <c r="K9" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L9" s="1">
         <v>326.8</v>
       </c>
-      <c r="M9" t="s">
-        <v>64</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="L9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10">
         <v>25.77</v>
       </c>
       <c r="G10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10">
         <v>1.22</v>
       </c>
       <c r="I10" s="1">
+        <v>31.439</v>
+      </c>
+      <c r="J10">
         <v>1.22</v>
       </c>
-      <c r="J10">
-        <v>31.4394</v>
-      </c>
       <c r="K10" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="L10" s="1">
-        <v>31.4394</v>
-      </c>
-      <c r="M10" t="s">
-        <v>64</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>31.439</v>
+      </c>
+      <c r="L10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11">
         <v>193.412</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H11">
         <v>1.406</v>
       </c>
       <c r="I11" s="1">
-        <v>1.406</v>
+        <v>271.937</v>
       </c>
       <c r="J11">
-        <v>271.937272</v>
+        <v>1.53</v>
       </c>
       <c r="K11" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L11" s="1">
-        <v>295.92036</v>
-      </c>
-      <c r="M11" t="s">
-        <v>65</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>295.92</v>
+      </c>
+      <c r="L11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12">
         <v>185</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H12">
         <v>1.406</v>
       </c>
       <c r="I12" s="1">
-        <v>1.406</v>
+        <v>260.11</v>
       </c>
       <c r="J12">
-        <v>260.11</v>
+        <v>1.52</v>
       </c>
       <c r="K12" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L12" s="1">
         <v>281.2</v>
       </c>
-      <c r="M12" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="L12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13">
         <v>265</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H13">
         <v>1.412</v>
       </c>
       <c r="I13" s="1">
-        <v>1.412</v>
+        <v>374.18</v>
       </c>
       <c r="J13">
-        <v>374.18</v>
+        <v>1.52</v>
       </c>
       <c r="K13" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L13" s="1">
         <v>402.8</v>
       </c>
-      <c r="M13" t="s">
-        <v>67</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="L13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F14">
         <v>128.132</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H14">
         <v>1.412</v>
       </c>
       <c r="I14" s="1">
-        <v>1.412</v>
+        <v>180.922</v>
       </c>
       <c r="J14">
-        <v>180.922384</v>
+        <v>1.52</v>
       </c>
       <c r="K14" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L14" s="1">
-        <v>194.76064</v>
-      </c>
-      <c r="M14" t="s">
-        <v>68</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>194.761</v>
+      </c>
+      <c r="L14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F15">
         <v>410</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H15">
         <v>1.412</v>
       </c>
       <c r="I15" s="1">
-        <v>1.412</v>
+        <v>578.92</v>
       </c>
       <c r="J15">
-        <v>578.92</v>
+        <v>1.56</v>
       </c>
       <c r="K15" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L15" s="1">
         <v>639.6</v>
       </c>
-      <c r="M15" t="s">
-        <v>69</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="L15" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F16">
         <v>155.268</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H16">
         <v>1.412</v>
       </c>
       <c r="I16" s="1">
-        <v>1.412</v>
+        <v>219.238</v>
       </c>
       <c r="J16">
-        <v>219.238416</v>
+        <v>1.53</v>
       </c>
       <c r="K16" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L16" s="1">
-        <v>237.56004</v>
-      </c>
-      <c r="M16" t="s">
-        <v>70</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>237.56</v>
+      </c>
+      <c r="L16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17">
         <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17">
         <v>1.437</v>
       </c>
       <c r="I17" s="1">
-        <v>1.437</v>
+        <v>158.07</v>
       </c>
       <c r="J17">
-        <v>158.07</v>
+        <v>1.54</v>
       </c>
       <c r="K17" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L17" s="1">
         <v>169.4</v>
       </c>
-      <c r="M17" t="s">
-        <v>71</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="L17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F18">
         <v>214.519</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H18">
         <v>1.451</v>
       </c>
       <c r="I18" s="1">
-        <v>1.451</v>
+        <v>311.267</v>
       </c>
       <c r="J18">
-        <v>311.267069</v>
+        <v>1.56</v>
       </c>
       <c r="K18" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L18" s="1">
-        <v>334.64964</v>
-      </c>
-      <c r="M18" t="s">
-        <v>72</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>334.65</v>
+      </c>
+      <c r="L18" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19">
         <v>249.462</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H19">
         <v>1.469</v>
       </c>
       <c r="I19" s="1">
-        <v>1.469</v>
+        <v>366.46</v>
       </c>
       <c r="J19">
-        <v>366.459678</v>
+        <v>1.56</v>
       </c>
       <c r="K19" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L19" s="1">
-        <v>389.16072</v>
-      </c>
-      <c r="M19" t="s">
-        <v>73</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>389.161</v>
+      </c>
+      <c r="L19" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F20">
         <v>345</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20">
         <v>1.469</v>
       </c>
       <c r="I20" s="1">
-        <v>1.469</v>
+        <v>506.805</v>
       </c>
       <c r="J20">
-        <v>506.805</v>
+        <v>1.56</v>
       </c>
       <c r="K20" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L20" s="1">
         <v>538.2</v>
       </c>
-      <c r="M20" t="s">
-        <v>74</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="L20" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F21">
         <v>25.262</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21">
         <v>1.22</v>
       </c>
       <c r="I21" s="1">
+        <v>30.82</v>
+      </c>
+      <c r="J21">
         <v>1.22</v>
       </c>
-      <c r="J21">
-        <v>30.81964</v>
-      </c>
       <c r="K21" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="L21" s="1">
-        <v>30.81964</v>
-      </c>
-      <c r="M21" t="s">
-        <v>74</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>30.82</v>
+      </c>
+      <c r="L21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22">
         <v>210.019</v>
       </c>
       <c r="G22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H22">
         <v>1.469</v>
       </c>
       <c r="I22" s="1">
-        <v>1.469</v>
+        <v>308.518</v>
       </c>
       <c r="J22">
-        <v>308.517911</v>
+        <v>1.56</v>
       </c>
       <c r="K22" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L22" s="1">
-        <v>327.62964</v>
-      </c>
-      <c r="M22" t="s">
-        <v>75</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>327.63</v>
+      </c>
+      <c r="L22" t="s">
+        <v>74</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F23">
         <v>166.09</v>
       </c>
       <c r="G23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H23">
         <v>1.469</v>
       </c>
       <c r="I23" s="1">
-        <v>1.469</v>
+        <v>243.986</v>
       </c>
       <c r="J23">
-        <v>243.98621</v>
+        <v>1.56</v>
       </c>
       <c r="K23" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L23" s="1">
-        <v>259.1004</v>
-      </c>
-      <c r="M23" t="s">
-        <v>76</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>259.1</v>
+      </c>
+      <c r="L23" t="s">
+        <v>75</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F24">
         <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H24">
         <v>1.489</v>
       </c>
       <c r="I24" s="1">
-        <v>1.489</v>
+        <v>96.785</v>
       </c>
       <c r="J24">
-        <v>96.785</v>
+        <v>1.58</v>
       </c>
       <c r="K24" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L24" s="1">
         <v>102.7</v>
       </c>
-      <c r="M24" t="s">
-        <v>77</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="L24" t="s">
+        <v>76</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F25">
         <v>215</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H25">
         <v>1.499</v>
       </c>
       <c r="I25" s="1">
-        <v>1.499</v>
+        <v>322.285</v>
       </c>
       <c r="J25">
-        <v>322.285</v>
+        <v>1.63</v>
       </c>
       <c r="K25" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L25" s="1">
         <v>350.45</v>
       </c>
-      <c r="M25" t="s">
-        <v>78</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="L25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F26">
         <v>128.221</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H26">
         <v>1.499</v>
       </c>
       <c r="I26" s="1">
-        <v>1.499</v>
+        <v>192.203</v>
       </c>
       <c r="J26">
-        <v>192.203279</v>
+        <v>1.63</v>
       </c>
       <c r="K26" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L26" s="1">
-        <v>209.00023</v>
-      </c>
-      <c r="M26" t="s">
-        <v>79</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>209</v>
+      </c>
+      <c r="L26" t="s">
+        <v>78</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F27">
         <v>265.012</v>
       </c>
       <c r="G27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H27">
         <v>1.528</v>
       </c>
       <c r="I27" s="1">
-        <v>1.528</v>
+        <v>404.938</v>
       </c>
       <c r="J27">
-        <v>404.938336</v>
+        <v>1.68</v>
       </c>
       <c r="K27" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L27" s="1">
-        <v>445.22016</v>
-      </c>
-      <c r="M27" t="s">
-        <v>80</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>445.22</v>
+      </c>
+      <c r="L27" t="s">
+        <v>79</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F28">
         <v>220.018</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H28">
         <v>1.588</v>
       </c>
       <c r="I28" s="1">
-        <v>1.588</v>
+        <v>349.389</v>
       </c>
       <c r="J28">
-        <v>349.388584</v>
+        <v>1.69</v>
       </c>
       <c r="K28" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L28" s="1">
-        <v>371.83042</v>
-      </c>
-      <c r="M28" t="s">
-        <v>81</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+        <v>371.83</v>
+      </c>
+      <c r="L28" t="s">
+        <v>80</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F29">
         <v>154.083</v>
       </c>
       <c r="G29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H29">
         <v>1.588</v>
       </c>
       <c r="I29" s="1">
-        <v>1.588</v>
+        <v>244.684</v>
       </c>
       <c r="J29">
-        <v>244.683804</v>
+        <v>1.69</v>
       </c>
       <c r="K29" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L29" s="1">
-        <v>260.40027</v>
-      </c>
-      <c r="M29" t="s">
-        <v>82</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+        <v>260.4</v>
+      </c>
+      <c r="L29" t="s">
+        <v>81</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F30">
         <v>310</v>
       </c>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H30">
         <v>1.588</v>
       </c>
       <c r="I30" s="1">
-        <v>1.588</v>
+        <v>492.28</v>
       </c>
       <c r="J30">
-        <v>492.28</v>
+        <v>1.7</v>
       </c>
       <c r="K30" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L30" s="1">
         <v>527</v>
       </c>
-      <c r="M30" t="s">
-        <v>83</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="L30" t="s">
+        <v>82</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F31">
         <v>22.697</v>
       </c>
       <c r="G31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H31">
         <v>1.22</v>
       </c>
       <c r="I31" s="1">
+        <v>27.69</v>
+      </c>
+      <c r="J31">
         <v>1.22</v>
       </c>
-      <c r="J31">
-        <v>27.69034</v>
-      </c>
       <c r="K31" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="L31" s="1">
-        <v>27.69034</v>
-      </c>
-      <c r="M31" t="s">
-        <v>83</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>27.69</v>
+      </c>
+      <c r="L31" t="s">
+        <v>82</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F32">
         <v>110.419</v>
       </c>
       <c r="G32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H32">
         <v>1.619</v>
       </c>
       <c r="I32" s="1">
-        <v>1.619</v>
+        <v>178.768</v>
       </c>
       <c r="J32">
-        <v>178.768361</v>
+        <v>1.72</v>
       </c>
       <c r="K32" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L32" s="1">
-        <v>189.92068</v>
-      </c>
-      <c r="M32" t="s">
-        <v>84</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+        <v>189.921</v>
+      </c>
+      <c r="L32" t="s">
+        <v>83</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F33">
         <v>270</v>
       </c>
       <c r="G33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H33">
         <v>1.619</v>
       </c>
       <c r="I33" s="1">
-        <v>1.619</v>
+        <v>437.13</v>
       </c>
       <c r="J33">
-        <v>437.13</v>
+        <v>1.75</v>
       </c>
       <c r="K33" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L33" s="1">
         <v>472.5</v>
       </c>
-      <c r="M33" t="s">
-        <v>85</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="L33" t="s">
+        <v>84</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F34">
         <v>22.082</v>
       </c>
       <c r="G34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H34">
         <v>1.22</v>
       </c>
       <c r="I34" s="1">
+        <v>26.94</v>
+      </c>
+      <c r="J34">
         <v>1.22</v>
       </c>
-      <c r="J34">
-        <v>26.94004</v>
-      </c>
       <c r="K34" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="L34" s="1">
-        <v>26.94004</v>
-      </c>
-      <c r="M34" t="s">
-        <v>85</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>26.94</v>
+      </c>
+      <c r="L34" t="s">
+        <v>84</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F35">
         <v>180</v>
       </c>
       <c r="G35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H35">
         <v>1.619</v>
       </c>
       <c r="I35" s="1">
-        <v>1.619</v>
+        <v>291.42</v>
       </c>
       <c r="J35">
-        <v>291.42</v>
+        <v>1.75</v>
       </c>
       <c r="K35" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L35" s="1">
         <v>315</v>
       </c>
-      <c r="M35" t="s">
-        <v>86</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="L35" t="s">
+        <v>85</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F36">
         <v>150</v>
       </c>
       <c r="G36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H36">
         <v>1.653</v>
       </c>
       <c r="I36" s="1">
-        <v>1.653</v>
+        <v>247.95</v>
       </c>
       <c r="J36">
-        <v>247.95</v>
+        <v>1.78</v>
       </c>
       <c r="K36" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L36" s="1">
         <v>267</v>
       </c>
-      <c r="M36" t="s">
-        <v>87</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="L36" t="s">
+        <v>86</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F37">
         <v>150.04</v>
       </c>
       <c r="G37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H37">
         <v>1.653</v>
       </c>
       <c r="I37" s="1">
-        <v>1.653</v>
+        <v>248.016</v>
       </c>
       <c r="J37">
-        <v>248.01612</v>
+        <v>1.75</v>
       </c>
       <c r="K37" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L37" s="1">
         <v>262.57</v>
       </c>
-      <c r="M37" t="s">
-        <v>88</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="L37" t="s">
+        <v>87</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F38">
         <v>210</v>
       </c>
       <c r="G38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H38">
         <v>1.674</v>
       </c>
       <c r="I38" s="1">
-        <v>1.674</v>
+        <v>351.54</v>
       </c>
       <c r="J38">
-        <v>351.54</v>
+        <v>1.75</v>
       </c>
       <c r="K38" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L38" s="1">
         <v>367.5</v>
       </c>
-      <c r="M38" t="s">
-        <v>89</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="L38" t="s">
+        <v>88</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F39">
         <v>100</v>
       </c>
       <c r="G39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H39">
         <v>1.674</v>
       </c>
       <c r="I39" s="1">
-        <v>1.674</v>
+        <v>167.4</v>
       </c>
       <c r="J39">
-        <v>167.4</v>
+        <v>1.79</v>
       </c>
       <c r="K39" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="L39" s="1">
         <v>179</v>
       </c>
-      <c r="M39" t="s">
-        <v>90</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="L39" t="s">
+        <v>89</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F40">
         <v>225.011</v>
       </c>
       <c r="G40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H40">
         <v>1.689</v>
       </c>
       <c r="I40" s="1">
-        <v>1.689</v>
+        <v>380.044</v>
       </c>
       <c r="J40">
-        <v>380.043579</v>
+        <v>1.78</v>
       </c>
       <c r="K40" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L40" s="1">
-        <v>400.51958</v>
-      </c>
-      <c r="M40" t="s">
-        <v>91</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+        <v>400.52</v>
+      </c>
+      <c r="L40" t="s">
+        <v>90</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F41">
         <v>26.516</v>
       </c>
       <c r="G41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H41">
         <v>1.22</v>
       </c>
       <c r="I41" s="1">
+        <v>32.35</v>
+      </c>
+      <c r="J41">
         <v>1.22</v>
       </c>
-      <c r="J41">
-        <v>32.34952</v>
-      </c>
       <c r="K41" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="L41" s="1">
-        <v>32.34952</v>
-      </c>
-      <c r="M41" t="s">
-        <v>91</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>32.35</v>
+      </c>
+      <c r="L41" t="s">
+        <v>90</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F42">
         <v>118.051</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H42">
         <v>1.689</v>
       </c>
       <c r="I42" s="1">
-        <v>1.689</v>
+        <v>199.388</v>
       </c>
       <c r="J42">
-        <v>199.388139</v>
+        <v>1.78</v>
       </c>
       <c r="K42" s="1">
-        <v>1.78</v>
-      </c>
-      <c r="L42" s="1">
-        <v>210.13078</v>
-      </c>
-      <c r="M42" t="s">
-        <v>92</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
+        <v>210.131</v>
+      </c>
+      <c r="L42" t="s">
+        <v>91</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="3" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
-      <c r="A45" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2821,69 +2692,69 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:14">
       <c r="A46" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="C46" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="E46" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="6">
         <v>7147.704</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="7">
         <v>36</v>
       </c>
       <c r="D47" s="7">
-        <v>1.495641</v>
-      </c>
-      <c r="E47" s="6">
+        <v>1.496</v>
+      </c>
+      <c r="E47" s="7">
         <v>10690.4</v>
       </c>
-      <c r="F47" s="6">
-        <v>11491</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="F47" s="7">
+        <v>11491.004</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="6">
         <v>122.327</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="7">
         <v>5</v>
       </c>
       <c r="D48" s="7">
         <v>1.22</v>
       </c>
-      <c r="E48" s="6">
-        <v>149.24</v>
-      </c>
-      <c r="F48" s="6">
-        <v>149.24</v>
+      <c r="E48" s="7">
+        <v>149.239</v>
+      </c>
+      <c r="F48" s="7">
+        <v>149.239</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" s="9">
         <v>7270.031</v>
@@ -2893,10 +2764,10 @@
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="9">
-        <v>10839.64</v>
+        <v>10839.639</v>
       </c>
       <c r="F49" s="9">
-        <v>11640.24</v>
+        <v>11640.243</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ЕВРОУЕЙ СЪРВИЗ ООД/ЕВРОУЕЙ СЪРВИЗ ООД.xlsx
@@ -769,10 +769,10 @@
         <v>45</v>
       </c>
       <c r="H2" s="1">
-        <v>1.699</v>
+        <v>1.7</v>
       </c>
       <c r="I2" s="1">
-        <v>424.767</v>
+        <v>425.017</v>
       </c>
       <c r="J2" s="1">
         <v>1.81</v>
@@ -813,10 +813,10 @@
         <v>45</v>
       </c>
       <c r="H3" s="1">
-        <v>1.707</v>
+        <v>1.71</v>
       </c>
       <c r="I3" s="1">
-        <v>281.655</v>
+        <v>282.15</v>
       </c>
       <c r="J3" s="1">
         <v>1.81</v>
@@ -857,10 +857,10 @@
         <v>45</v>
       </c>
       <c r="H4" s="1">
-        <v>1.707</v>
+        <v>1.71</v>
       </c>
       <c r="I4" s="1">
-        <v>367.62</v>
+        <v>368.266</v>
       </c>
       <c r="J4" s="1">
         <v>1.81</v>
@@ -901,10 +901,10 @@
         <v>45</v>
       </c>
       <c r="H5" s="1">
-        <v>1.707</v>
+        <v>1.71</v>
       </c>
       <c r="I5" s="1">
-        <v>281.655</v>
+        <v>282.15</v>
       </c>
       <c r="J5" s="1">
         <v>1.8</v>
@@ -989,10 +989,10 @@
         <v>45</v>
       </c>
       <c r="H7" s="1">
-        <v>1.707</v>
+        <v>1.71</v>
       </c>
       <c r="I7" s="1">
-        <v>399.438</v>
+        <v>400.14</v>
       </c>
       <c r="J7" s="1">
         <v>1.8</v>
@@ -1033,10 +1033,10 @@
         <v>45</v>
       </c>
       <c r="H8" s="1">
-        <v>1.693</v>
+        <v>1.69</v>
       </c>
       <c r="I8" s="1">
-        <v>186.23</v>
+        <v>185.9</v>
       </c>
       <c r="J8" s="1">
         <v>1.8</v>
@@ -1077,10 +1077,10 @@
         <v>45</v>
       </c>
       <c r="H9" s="1">
-        <v>1.693</v>
+        <v>1.69</v>
       </c>
       <c r="I9" s="1">
-        <v>33.86</v>
+        <v>33.8</v>
       </c>
       <c r="J9" s="1">
         <v>1.8</v>
@@ -1121,10 +1121,10 @@
         <v>45</v>
       </c>
       <c r="H10" s="1">
-        <v>1.693</v>
+        <v>1.69</v>
       </c>
       <c r="I10" s="1">
-        <v>406.32</v>
+        <v>405.6</v>
       </c>
       <c r="J10" s="1">
         <v>1.8</v>
@@ -1165,10 +1165,10 @@
         <v>45</v>
       </c>
       <c r="H11" s="1">
-        <v>1.687</v>
+        <v>1.69</v>
       </c>
       <c r="I11" s="1">
-        <v>379.575</v>
+        <v>380.25</v>
       </c>
       <c r="J11" s="1">
         <v>1.8</v>
@@ -1209,10 +1209,10 @@
         <v>45</v>
       </c>
       <c r="H12" s="1">
-        <v>1.687</v>
+        <v>1.69</v>
       </c>
       <c r="I12" s="1">
-        <v>312.095</v>
+        <v>312.65</v>
       </c>
       <c r="J12" s="1">
         <v>1.8</v>
@@ -1253,10 +1253,10 @@
         <v>45</v>
       </c>
       <c r="H13" s="1">
-        <v>1.719</v>
+        <v>1.72</v>
       </c>
       <c r="I13" s="1">
-        <v>171.9</v>
+        <v>172</v>
       </c>
       <c r="J13" s="1">
         <v>1.87</v>
@@ -1297,10 +1297,10 @@
         <v>45</v>
       </c>
       <c r="H14" s="1">
-        <v>1.719</v>
+        <v>1.72</v>
       </c>
       <c r="I14" s="1">
-        <v>317.448</v>
+        <v>317.632</v>
       </c>
       <c r="J14" s="1">
         <v>1.84</v>
@@ -1341,10 +1341,10 @@
         <v>45</v>
       </c>
       <c r="H15" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I15" s="1">
-        <v>453.411</v>
+        <v>453.67</v>
       </c>
       <c r="J15" s="1">
         <v>1.85</v>
@@ -1385,10 +1385,10 @@
         <v>45</v>
       </c>
       <c r="H16" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I16" s="1">
-        <v>143.278</v>
+        <v>143.36</v>
       </c>
       <c r="J16" s="1">
         <v>1.85</v>
@@ -1429,10 +1429,10 @@
         <v>45</v>
       </c>
       <c r="H17" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I17" s="1">
-        <v>122.447</v>
+        <v>122.518</v>
       </c>
       <c r="J17" s="1">
         <v>1.85</v>
@@ -1517,10 +1517,10 @@
         <v>45</v>
       </c>
       <c r="H19" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I19" s="1">
-        <v>655.8920000000001</v>
+        <v>656.2670000000001</v>
       </c>
       <c r="J19" s="1">
         <v>1.87</v>
@@ -1561,10 +1561,10 @@
         <v>45</v>
       </c>
       <c r="H20" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I20" s="1">
-        <v>374.146</v>
+        <v>374.36</v>
       </c>
       <c r="J20" s="1">
         <v>1.87</v>
@@ -1605,10 +1605,10 @@
         <v>45</v>
       </c>
       <c r="H21" s="1">
-        <v>1.749</v>
+        <v>1.75</v>
       </c>
       <c r="I21" s="1">
-        <v>363.792</v>
+        <v>364</v>
       </c>
       <c r="J21" s="1">
         <v>1.84</v>
@@ -1667,10 +1667,10 @@
         <v>18</v>
       </c>
       <c r="D26" s="8">
-        <v>1.71874</v>
+        <v>1.72001</v>
       </c>
       <c r="E26" s="6">
-        <v>5675.53</v>
+        <v>5679.73</v>
       </c>
       <c r="F26" s="6">
         <v>6034.65</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="10">
-        <v>5728.35</v>
+        <v>5732.55</v>
       </c>
       <c r="F28" s="10">
         <v>6087.47</v>
